--- a/Configuration.xlsx
+++ b/Configuration.xlsx
@@ -1877,7 +1877,7 @@
         <v>64</v>
       </c>
       <c r="B2" s="8">
-        <f>SUM(INVENTAIRE!I2:I5)</f>
+        <f>SUM(INVENTAIRE!H2:H5)</f>
         <v>0</v>
       </c>
       <c r="C2" s="7" t="s">
@@ -1889,7 +1889,7 @@
         <v>65</v>
       </c>
       <c r="B3" s="8">
-        <f>SUMIF(INVENTAIRE!I2:I5,"&gt;=0",INVENTAIRE!J2:J5)</f>
+        <f>SUMIF(INVENTAIRE!H2:H5,"&gt;=0",INVENTAIRE!I2:I5)</f>
         <v>0</v>
       </c>
       <c r="C3" s="7" t="s">
@@ -1928,7 +1928,7 @@
         <v>69</v>
       </c>
       <c r="B8" s="8">
-        <f>SUM(INVENTAIRE!L2:L5)</f>
+        <f>SUM(INVENTAIRE!K2:K5)</f>
         <v>0</v>
       </c>
       <c r="C8" s="7" t="s">
